--- a/result/organelle_protein_abundance_range.xlsx
+++ b/result/organelle_protein_abundance_range.xlsx
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.002278437348706463</v>
+        <v>0.002278437348706464</v>
       </c>
       <c r="C3" t="n">
         <v>0.001172643399589614</v>
@@ -593,7 +593,7 @@
         <v>3.789271378345713e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0001020630573221589</v>
+        <v>0.0001020630573221588</v>
       </c>
       <c r="J3" t="n">
         <v>4.359316535518397e-05</v>
@@ -636,7 +636,7 @@
         <v>0.0002811332104792682</v>
       </c>
       <c r="E4" t="n">
-        <v>9.515211849529437e-05</v>
+        <v>9.515211849529439e-05</v>
       </c>
       <c r="F4" t="n">
         <v>0.0001416507357193403</v>
@@ -660,7 +660,7 @@
         <v>5.92231243473126e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>9.333755023032917e-06</v>
+        <v>9.333755023032919e-06</v>
       </c>
       <c r="N4" t="n">
         <v>1.160510165471486e-06</v>
@@ -682,22 +682,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001132055144528843</v>
+        <v>0.001132055144528844</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0005936492824849146</v>
+        <v>0.0005936492824849148</v>
       </c>
       <c r="D5" t="n">
         <v>0.0004798122103503246</v>
       </c>
       <c r="E5" t="n">
-        <v>7.076641610926601e-05</v>
+        <v>7.0766416109266e-05</v>
       </c>
       <c r="F5" t="n">
         <v>4.231031597907948e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>2.525939137873163e-05</v>
+        <v>2.525939137873165e-05</v>
       </c>
       <c r="H5" t="n">
         <v>8.305747670695093e-06</v>
@@ -712,7 +712,7 @@
         <v>1.455237620714e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>6.427842627878001e-06</v>
+        <v>6.427842627878e-06</v>
       </c>
       <c r="M5" t="n">
         <v>2.233337297480488e-06</v>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001300133448244143</v>
+        <v>0.001300133448244142</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0009681980871416541</v>
+        <v>0.0009681980871416539</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0005938202675912893</v>
+        <v>0.0005938202675912888</v>
       </c>
       <c r="E6" t="n">
         <v>0.000129159987611482</v>
@@ -758,7 +758,7 @@
         <v>1.384109567062146e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.006317654285659e-05</v>
+        <v>1.00631765428566e-05</v>
       </c>
       <c r="J6" t="n">
         <v>2.076603338045386e-05</v>
@@ -798,16 +798,16 @@
         <v>0.001035915855783454</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0006933205638113998</v>
+        <v>0.0006933205638113997</v>
       </c>
       <c r="E7" t="n">
-        <v>0.000233754460725607</v>
+        <v>0.0002337544607256071</v>
       </c>
       <c r="F7" t="n">
         <v>0.000198566327204517</v>
       </c>
       <c r="G7" t="n">
-        <v>7.168979976017901e-05</v>
+        <v>7.168979976017899e-05</v>
       </c>
       <c r="H7" t="n">
         <v>3.121583026661667e-05</v>
@@ -825,7 +825,7 @@
         <v>1.518633233351035e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>7.49437458636e-06</v>
+        <v>7.494374586360001e-06</v>
       </c>
       <c r="N7" t="n">
         <v>1.074338703471e-06</v>
@@ -847,13 +847,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002734044531691887</v>
+        <v>0.002734044531691886</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001385480393746902</v>
+        <v>0.001385480393746903</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001024012221360076</v>
+        <v>0.001024012221360075</v>
       </c>
       <c r="E8" t="n">
         <v>0.0002913681525365021</v>
@@ -868,13 +868,13 @@
         <v>4.961028278891936e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0001902971856923691</v>
+        <v>0.000190297185692369</v>
       </c>
       <c r="J8" t="n">
         <v>5.351000041705787e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>6.616613654764339e-05</v>
+        <v>6.616613654764338e-05</v>
       </c>
       <c r="L8" t="n">
         <v>3.842292372722671e-05</v>
@@ -902,13 +902,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.005959005379741445</v>
+        <v>0.005959005379741454</v>
       </c>
       <c r="C9" t="n">
-        <v>0.002698702211308841</v>
+        <v>0.002698702211308842</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001800835855612344</v>
+        <v>0.001800835855612345</v>
       </c>
       <c r="E9" t="n">
         <v>0.000515885334817123</v>
@@ -929,7 +929,7 @@
         <v>0.0001636388651370349</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0001471686852333628</v>
+        <v>0.0001471686852333627</v>
       </c>
       <c r="L9" t="n">
         <v>0.000386822364174485</v>
@@ -941,7 +941,7 @@
         <v>6.224908320812887e-06</v>
       </c>
       <c r="O9" t="n">
-        <v>8.005476573417074e-07</v>
+        <v>8.005476573417073e-07</v>
       </c>
       <c r="P9" t="n">
         <v>3.194072918844861e-06</v>
